--- a/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent. Faustine dit : je suis surprise. Papa dit : d'abord respirer. Ensuite comprendre. Faustine souffle une grande fois. Elle regarde le ballon. Elle dit : je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit. Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux. Papa dit : tu as soufflé. Faustine hoche la tête.</t>
+          <t>Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent. Je suis surprise. D'abord respirer. Ensuite comprendre. Faustine souffle une grande fois. Elle regarde le ballon. Je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit. Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux. Tu as soufflé. Faustine hoche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent.
+enfant-f|Je suis surprise.
+papa|D'abord respirer. Ensuite comprendre.
+narrateur|Faustine souffle une grande fois. Elle regarde le ballon.
+narrateur|Je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit.
+narrateur|Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux.
+papa|Tu as soufflé.
+narrateur|Faustine hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine a nommé : surpris. Elle a soufflé. Elle a voulu comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon reste dans le salon. Faustine s'assoit près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Faustine hoche la tête.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Faustine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Faustine a nommé : surpris. Elle a soufflé. Elle a voulu comprendre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Le ballon reste dans le salon. Faustine s'assoit près de papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faustine est surprise</t>
+          <t>Le ballon de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Papa ouvre une boîte. Un ballon sort. Mila est surprise. Elle souffle. Elle comprend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent. Je suis surprise. D'abord respirer. Ensuite comprendre. Faustine souffle une grande fois. Elle regarde le ballon. Je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit. Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux. Tu as soufflé. Faustine hoche la tête.</t>
+          <t>Une boîte attend sous la table. Le ruban est rouge. Un rayon traverse le salon. Des poussières dansent. Le tapis est tout doux. Le canapé sent le soleil. Un rideau bouge un peu. Un livre attend sur la table. Le livre a une couverture bleue. Le salon est calme. Je plie une chaussette. La chaussette est jaune. Mila, tu vois la boîte ? Oui. Elle est grande. Le ruban brille. En ce moment, papa ouvre la boîte. Un ballon sort. Pop. Mila sent son cœur vite. Ses yeux s'ouvrent. Je suis surprise. D'abord respirer. Ensuite comprendre. Mila souffle une grande fois. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Mila regarde le ballon. Le ballon est rond. Il est un peu jaune. C'est un ballon. Rien n'est cassé. On peut respirer. Mila souffle encore. Elle touche le ballon. Il est doux. Tu as soufflé. Oui. Je comprends. Être surpris, on peut respirer. Puis on cherche à comprendre. Mila hoche la tête. Une ficelle traîne. La ficelle est rouge aussi. C'est doux, papa. Oui. On regarde ensemble. Tu as nommé : surprise. Mila s'assoit sur le tapis. Le rayon reste sur le tapis. Des poussières dansent encore. Tu as respiré. Tu as regardé. Pop. Puis calme. On peut rester sur le tapis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent.
+          <t>narrateur|Une boîte attend sous la table.
+narrateur|Le ruban est rouge.
+narrateur|Un rayon traverse le salon.
+narrateur|Des poussières dansent.
+narrateur|Le tapis est tout doux.
+narrateur|Le canapé sent le soleil.
+narrateur|Un rideau bouge un peu.
+narrateur|Un livre attend sur la table.
+narrateur|Le livre a une couverture bleue.
+maman|Le salon est calme.
+maman|Je plie une chaussette.
+narrateur|La chaussette est jaune.
+papa|Mila, tu vois la boîte ?
+enfant-f|Oui. Elle est grande.
+maman|Le ruban brille.
+narrateur|En ce moment, papa ouvre la boîte.
+narrateur|Un ballon sort.
+narrateur|Pop.
+narrateur|Mila sent son cœur vite.
+narrateur|Ses yeux s'ouvrent.
 enfant-f|Je suis surprise.
-papa|D'abord respirer. Ensuite comprendre.
-narrateur|Faustine souffle une grande fois. Elle regarde le ballon.
-narrateur|Je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit.
-narrateur|Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux.
+papa|D'abord respirer.
+papa|Ensuite comprendre.
+narrateur|Mila souffle une grande fois.
+maman|Tu as soufflé. Bravo.
+papa|Qu'est-ce que tu vois ?
+enfant-f|Je veux comprendre.
+narrateur|Mila regarde le ballon.
+narrateur|Le ballon est rond.
+narrateur|Il est un peu jaune.
+enfant-f|C'est un ballon.
+papa|Rien n'est cassé.
+maman|On peut respirer.
+narrateur|Mila souffle encore.
+narrateur|Elle touche le ballon.
+narrateur|Il est doux.
 papa|Tu as soufflé.
-narrateur|Faustine hoche la tête.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Oui. Je comprends.
+maman|Être surpris, on peut respirer.
+papa|Puis on cherche à comprendre.
+narrateur|Mila hoche la tête.
+narrateur|Une ficelle traîne.
+narrateur|La ficelle est rouge aussi.
+enfant-f|C'est doux, papa.
+papa|Oui. On regarde ensemble.
+maman|Tu as nommé : surprise.
+narrateur|Mila s'assoit sur le tapis.
+narrateur|Le rayon reste sur le tapis.
+narrateur|Des poussières dansent encore.
+papa|Tu as respiré. Tu as regardé.
+enfant-f|Pop. Puis calme.
+maman|On peut rester sur le tapis.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>salon,ballon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Faustine est surprise. Que fait-elle d'abord ?</t>
+          <t>Mila est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Faustine est surprise. Que fait-elle d'abord ?</t>
+          <t>narrateur|Mila est surprise.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Faustine a nommé : surpris. Elle a soufflé. Elle a voulu comprendre.</t>
+          <t>Mila a nommé : surpris. Elle a soufflé. Elle a voulu comprendre. Tu as respiré. Bravo. Tu as regardé le ballon. C'est un ballon. Il est doux. Rien n'était cassé. On souffle. On comprend. Mila pose le ballon. Le ballon fait un petit bruit. On le laisse sur le tapis ? Oui. Il est calme. La chaussette est pliée. Le ruban reste rouge. Le livre attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,10 +1740,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Faustine a nommé : surpris. Elle a soufflé. Elle a voulu comprendre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a nommé : surpris.
+narrateur|Elle a soufflé.
+narrateur|Elle a voulu comprendre.
+papa|Tu as respiré. Bravo.
+maman|Tu as regardé le ballon.
+enfant-f|C'est un ballon. Il est doux.
+papa|Rien n'était cassé.
+maman|On souffle. On comprend.
+narrateur|Mila pose le ballon.
+narrateur|Le ballon fait un petit bruit.
+papa|On le laisse sur le tapis ?
+enfant-f|Oui. Il est calme.
+maman|La chaussette est pliée.
+narrateur|Le ruban reste rouge.
+narrateur|Le livre attend encore.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>salon</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le ballon reste dans le salon. Faustine s'assoit près de papa.</t>
+          <t>Le ballon reste dans le salon. Mila s'assoit près de papa. Tu me prends la main ? Oui, papa. Le tapis est doux. Le ballon est jaune. Tu as soufflé. C'est bien. On range la boîte ? Oui. Le ruban aussi. Bravo, Mila. Ils restent un moment. Le rayon glisse un peu. La boîte est ouverte. Le canapé sent encore le soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1922,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le ballon reste dans le salon. Faustine s'assoit près de papa.</t>
+          <t>narrateur|Le ballon reste dans le salon.
+narrateur|Mila s'assoit près de papa.
+papa|Tu me prends la main ?
+enfant-f|Oui, papa.
+maman|Le tapis est doux.
+enfant-f|Le ballon est jaune.
+papa|Tu as soufflé. C'est bien.
+maman|On range la boîte ?
+enfant-f|Oui. Le ruban aussi.
+papa|Bravo, Mila.
+narrateur|Ils restent un moment.
+narrateur|Le rayon glisse un peu.
+narrateur|La boîte est ouverte.
+narrateur|Le canapé sent encore le soleil.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le ballon est resté doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2103,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais surprise. J'ai soufflé.
+papa|Tu as compris. Bravo.
+maman|Le ballon est resté doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Faustine est dans le salon. Papa ouvre une boîte. Un ballon sort. Pop. Faustine sent son cœur vite. Ses yeux s'ouvrent. Faustine dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Papa dit : d'abord respirer. Ensuite comprendre. Faustine souffle une grande fois. Elle regarde le ballon. Elle dit : je veux comprendre. Elle voit le ballon. Rien n'est cassé. Papa sourit. Faustine souffle encore. Être surpris, on peut respirer. Puis on cherche à comprendre. Faustine touche le ballon. Il est doux. Papa dit : tu as soufflé. Faustine hoche la tête.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une boîte attend sous la table. Le ruban est rouge. Un rayon traverse le salon. Des poussières dansent. Le tapis est tout doux. Le canapé sent le soleil. Un rideau bouge un peu. Un livre attend sur la table. Le livre a une couverture bleue. Le salon est calme. Je plie une chaussette. La chaussette est jaune. Mila, tu vois la boîte ? Oui. Elle est grande. Le ruban brille. En ce moment, papa ouvre la boîte. Un ballon sort. Pop. Mila sent son cœur vite. Ses yeux s'ouvrent. Je suis surprise. D'abord respirer. Ensuite comprendre. Mila souffle une grande fois. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Mila regarde le ballon. Le ballon est rond. Il est un peu jaune. C'est un ballon. Rien n'est cassé. On peut respirer. Mila souffle encore. Elle touche le ballon. Il est doux. Tu as soufflé. Oui. Je comprends. Être surpris, on peut respirer. Puis on cherche à comprendre. Mila hoche la tête. Une ficelle traîne. La ficelle est rouge aussi. C'est doux, papa. Oui. On regarde ensemble. Tu as nommé : surprise. Mila s'assoit sur le tapis. Le rayon reste sur le tapis. Des poussières dansent encore. Tu as respiré. Tu as regardé. Pop. Puis calme. On peut rester sur le tapis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Faustine est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Faustine a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Elle a soufflé. Elle a voulu comprendre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a nommé : surpris. Elle a soufflé. Elle a voulu comprendre. Tu as respiré. Bravo. Tu as regardé le ballon. C'est un ballon. Il est doux. Rien n'était cassé. On souffle. On comprend. Mila pose le ballon. Le ballon fait un petit bruit. On le laisse sur le tapis ? Oui. Il est calme. La chaussette est pliée. Le ruban reste rouge. Le livre attend encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1791,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le ballon reste dans le salon. Faustine s'assoit près de papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon reste dans le salon. Mila s'assoit près de papa. Tu me prends la main ? Oui, papa. Le tapis est doux. Le ballon est jaune. Tu as soufflé. C'est bien. On range la boîte ? Oui. Le ruban aussi. Bravo, Mila. Ils restent un moment. Le rayon glisse un peu. La boîte est ouverte. Le canapé sent encore le soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1937,6 @@
 narrateur|Le canapé sent encore le soleil.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le ballon est resté doux. L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le ballon est resté doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le ballon est resté doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,11 +2103,9 @@
         <is>
           <t>enfant-f|J'étais surprise. J'ai soufflé.
 papa|Tu as compris. Bravo.
-maman|Le ballon est resté doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le ballon est resté doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faustine, papa</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
